--- a/cfg/excel/EquipCfg.xlsx
+++ b/cfg/excel/EquipCfg.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Shooting\Luban\Config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\IdeaProjects\server-cluster\cfg\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="31950" windowHeight="16890"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <t>id</t>
   </si>
   <si>
-    <t>gearName</t>
+    <t>equiqName</t>
   </si>
   <si>
     <t>icon</t>
